--- a/ONCHO/Entomological survey Survey/Nigeria/2026/delta/ng_oncho_2605_1_community_del.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2026/delta/ng_oncho_2605_1_community_del.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2026\delta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91892D10-A3A7-4E0D-B70C-1EB6D7EB59DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E868AC-8927-42E3-B93E-5D826994869B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -242,12 +242,6 @@
     <t>site_id</t>
   </si>
   <si>
-    <t>ng_oncho_2605_1_community_del</t>
-  </si>
-  <si>
-    <t>(2026 Delta) 1. Community Registration Form</t>
-  </si>
-  <si>
     <t>ABIA</t>
   </si>
   <si>
@@ -1362,6 +1356,12 @@
   </si>
   <si>
     <t>ABI_ARO_E_055</t>
+  </si>
+  <si>
+    <t>ng_oncho_2605_1_community_del_v2</t>
+  </si>
+  <si>
+    <t>(2026 - Delta, Anambra, Abia) 1. Community Registration Form</t>
   </si>
 </sst>
 </file>
@@ -2337,10 +2337,10 @@
         <v>56</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2348,10 +2348,10 @@
         <v>56</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2359,10 +2359,10 @@
         <v>56</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2370,13 +2370,13 @@
         <v>57</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2384,13 +2384,13 @@
         <v>57</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2398,13 +2398,13 @@
         <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2412,13 +2412,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2426,13 +2426,13 @@
         <v>57</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2440,13 +2440,13 @@
         <v>57</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2454,13 +2454,13 @@
         <v>57</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2468,13 +2468,13 @@
         <v>57</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2482,13 +2482,13 @@
         <v>57</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2496,13 +2496,13 @@
         <v>57</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2510,13 +2510,13 @@
         <v>57</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2524,13 +2524,13 @@
         <v>57</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2538,13 +2538,13 @@
         <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2552,13 +2552,13 @@
         <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2566,13 +2566,13 @@
         <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2580,13 +2580,13 @@
         <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2594,13 +2594,13 @@
         <v>57</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2608,13 +2608,13 @@
         <v>57</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2622,13 +2622,13 @@
         <v>57</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2636,13 +2636,13 @@
         <v>57</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2650,13 +2650,13 @@
         <v>57</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2664,13 +2664,13 @@
         <v>57</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2678,13 +2678,13 @@
         <v>57</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2692,13 +2692,13 @@
         <v>57</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2706,13 +2706,13 @@
         <v>57</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2720,13 +2720,13 @@
         <v>57</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2734,13 +2734,13 @@
         <v>57</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2748,13 +2748,13 @@
         <v>57</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2762,13 +2762,13 @@
         <v>57</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2776,13 +2776,13 @@
         <v>57</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2790,13 +2790,13 @@
         <v>57</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -2804,13 +2804,13 @@
         <v>57</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2818,13 +2818,13 @@
         <v>57</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2832,13 +2832,13 @@
         <v>57</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2846,13 +2846,13 @@
         <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2860,13 +2860,13 @@
         <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D45" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2874,13 +2874,13 @@
         <v>57</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2888,13 +2888,13 @@
         <v>57</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D47" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2902,13 +2902,13 @@
         <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2916,13 +2916,13 @@
         <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2930,13 +2930,13 @@
         <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2947,13 +2947,13 @@
         <v>62</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -2961,13 +2961,13 @@
         <v>62</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E53" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -2975,13 +2975,13 @@
         <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2989,13 +2989,13 @@
         <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E55" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3003,13 +3003,13 @@
         <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E56" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3017,13 +3017,13 @@
         <v>62</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E57" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3031,13 +3031,13 @@
         <v>62</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E58" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3045,13 +3045,13 @@
         <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E59" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3059,13 +3059,13 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E60" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3073,13 +3073,13 @@
         <v>62</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -3087,13 +3087,13 @@
         <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3101,13 +3101,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -3115,13 +3115,13 @@
         <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E64" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3129,13 +3129,13 @@
         <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E65" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3143,13 +3143,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E66" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3157,13 +3157,13 @@
         <v>62</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E67" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -3171,13 +3171,13 @@
         <v>62</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E68" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3185,13 +3185,13 @@
         <v>62</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E69" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3199,13 +3199,13 @@
         <v>62</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E70" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3213,13 +3213,13 @@
         <v>62</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E71" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3227,13 +3227,13 @@
         <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E72" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3241,13 +3241,13 @@
         <v>62</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E73" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3255,13 +3255,13 @@
         <v>62</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E74" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3269,13 +3269,13 @@
         <v>62</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E75" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3283,13 +3283,13 @@
         <v>62</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E76" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3297,13 +3297,13 @@
         <v>62</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E77" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -3311,13 +3311,13 @@
         <v>62</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E78" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3325,13 +3325,13 @@
         <v>62</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3339,13 +3339,13 @@
         <v>62</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E80" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3353,13 +3353,13 @@
         <v>62</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E81" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3367,13 +3367,13 @@
         <v>62</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E82" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3381,13 +3381,13 @@
         <v>62</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E83" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3395,13 +3395,13 @@
         <v>62</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E84" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3409,13 +3409,13 @@
         <v>62</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E85" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3423,13 +3423,13 @@
         <v>62</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E86" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -3437,13 +3437,13 @@
         <v>62</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E87" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3451,13 +3451,13 @@
         <v>62</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E88" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3465,13 +3465,13 @@
         <v>62</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E89" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3479,13 +3479,13 @@
         <v>62</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E90" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3493,13 +3493,13 @@
         <v>62</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E91" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3507,13 +3507,13 @@
         <v>62</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E92" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -3521,13 +3521,13 @@
         <v>62</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E93" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -3535,13 +3535,13 @@
         <v>62</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E94" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3549,13 +3549,13 @@
         <v>62</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E95" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3563,13 +3563,13 @@
         <v>62</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E96" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -3577,13 +3577,13 @@
         <v>62</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E97" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -3591,13 +3591,13 @@
         <v>62</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E98" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -3605,13 +3605,13 @@
         <v>62</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E99" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -3619,13 +3619,13 @@
         <v>62</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E100" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -3633,13 +3633,13 @@
         <v>62</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E101" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -3647,13 +3647,13 @@
         <v>62</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E102" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3661,13 +3661,13 @@
         <v>62</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E103" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -3675,13 +3675,13 @@
         <v>62</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E104" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -3689,13 +3689,13 @@
         <v>62</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E105" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -3703,13 +3703,13 @@
         <v>62</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E106" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -3717,13 +3717,13 @@
         <v>62</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E107" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -3731,13 +3731,13 @@
         <v>62</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E108" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3745,13 +3745,13 @@
         <v>62</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E109" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3759,13 +3759,13 @@
         <v>62</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E110" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -3773,13 +3773,13 @@
         <v>62</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E111" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -3787,13 +3787,13 @@
         <v>62</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E112" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -3801,13 +3801,13 @@
         <v>62</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E113" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3815,13 +3815,13 @@
         <v>62</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E114" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -3829,13 +3829,13 @@
         <v>62</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E115" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3843,13 +3843,13 @@
         <v>62</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E116" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -3857,13 +3857,13 @@
         <v>62</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E117" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -3871,13 +3871,13 @@
         <v>62</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E118" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -3885,13 +3885,13 @@
         <v>62</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E119" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3899,13 +3899,13 @@
         <v>62</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E120" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -3913,13 +3913,13 @@
         <v>62</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E121" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -3927,13 +3927,13 @@
         <v>62</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E122" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -3941,13 +3941,13 @@
         <v>62</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E123" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3955,13 +3955,13 @@
         <v>62</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E124" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -3969,13 +3969,13 @@
         <v>62</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E125" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -3983,13 +3983,13 @@
         <v>62</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E126" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -3997,13 +3997,13 @@
         <v>62</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E127" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -4011,13 +4011,13 @@
         <v>62</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E128" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4025,13 +4025,13 @@
         <v>62</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E129" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="63" x14ac:dyDescent="0.25">
@@ -4039,13 +4039,13 @@
         <v>62</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E130" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -4053,13 +4053,13 @@
         <v>62</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E131" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -4067,13 +4067,13 @@
         <v>62</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E132" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -4081,13 +4081,13 @@
         <v>62</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E133" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4095,13 +4095,13 @@
         <v>62</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E134" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -4109,13 +4109,13 @@
         <v>62</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E135" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -4123,13 +4123,13 @@
         <v>62</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E136" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4137,13 +4137,13 @@
         <v>62</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E137" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -4151,13 +4151,13 @@
         <v>62</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E138" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -4165,13 +4165,13 @@
         <v>62</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E139" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -4179,13 +4179,13 @@
         <v>62</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E140" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4193,13 +4193,13 @@
         <v>62</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E141" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -4207,13 +4207,13 @@
         <v>62</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E142" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -4221,13 +4221,13 @@
         <v>62</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E143" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4235,13 +4235,13 @@
         <v>62</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E144" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="63" x14ac:dyDescent="0.25">
@@ -4249,13 +4249,13 @@
         <v>62</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E145" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -4263,13 +4263,13 @@
         <v>62</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E146" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -4277,13 +4277,13 @@
         <v>62</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E147" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -4291,13 +4291,13 @@
         <v>62</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E148" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -4305,13 +4305,13 @@
         <v>62</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E149" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4319,13 +4319,13 @@
         <v>62</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E150" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -4333,13 +4333,13 @@
         <v>62</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E151" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -4347,13 +4347,13 @@
         <v>62</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E152" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4361,13 +4361,13 @@
         <v>62</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E153" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -4375,13 +4375,13 @@
         <v>62</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E154" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -4389,13 +4389,13 @@
         <v>62</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E155" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -4403,13 +4403,13 @@
         <v>62</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E156" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -4417,13 +4417,13 @@
         <v>62</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E157" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -4431,13 +4431,13 @@
         <v>62</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E158" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4445,13 +4445,13 @@
         <v>62</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E159" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -4459,13 +4459,13 @@
         <v>62</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E160" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -4473,13 +4473,13 @@
         <v>62</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E161" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4487,13 +4487,13 @@
         <v>62</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E162" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -4501,13 +4501,13 @@
         <v>62</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E163" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4515,13 +4515,13 @@
         <v>62</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E164" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4529,13 +4529,13 @@
         <v>62</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E165" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4543,13 +4543,13 @@
         <v>62</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E166" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -4557,13 +4557,13 @@
         <v>62</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E167" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4571,13 +4571,13 @@
         <v>62</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E168" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -4585,13 +4585,13 @@
         <v>62</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E169" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -4599,13 +4599,13 @@
         <v>62</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4613,13 +4613,13 @@
         <v>62</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E171" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4627,13 +4627,13 @@
         <v>62</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E172" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4641,13 +4641,13 @@
         <v>62</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E173" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -4655,13 +4655,13 @@
         <v>62</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E174" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4669,13 +4669,13 @@
         <v>62</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E175" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -4683,13 +4683,13 @@
         <v>62</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E176" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -4697,13 +4697,13 @@
         <v>62</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E177" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -4711,13 +4711,13 @@
         <v>62</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E178" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -4725,13 +4725,13 @@
         <v>62</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E179" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4739,13 +4739,13 @@
         <v>62</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E180" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4753,13 +4753,13 @@
         <v>62</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E181" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4767,13 +4767,13 @@
         <v>62</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E182" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -4781,13 +4781,13 @@
         <v>62</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E183" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -4795,13 +4795,13 @@
         <v>62</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E184" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -4809,13 +4809,13 @@
         <v>62</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E185" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -4823,13 +4823,13 @@
         <v>62</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E186" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -4837,13 +4837,13 @@
         <v>62</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E187" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -4851,13 +4851,13 @@
         <v>62</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E188" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4865,13 +4865,13 @@
         <v>62</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E189" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -4879,13 +4879,13 @@
         <v>62</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E190" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -4893,13 +4893,13 @@
         <v>62</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E191" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -4907,13 +4907,13 @@
         <v>62</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E192" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -4921,13 +4921,13 @@
         <v>62</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E193" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -4935,13 +4935,13 @@
         <v>62</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E194" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -4949,13 +4949,13 @@
         <v>62</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E195" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4963,13 +4963,13 @@
         <v>62</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E196" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -4977,13 +4977,13 @@
         <v>62</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E197" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="63" x14ac:dyDescent="0.25">
@@ -4991,13 +4991,13 @@
         <v>62</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E198" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -5005,13 +5005,13 @@
         <v>62</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E199" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -5019,13 +5019,13 @@
         <v>62</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E200" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
@@ -5033,13 +5033,13 @@
         <v>62</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E201" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -5047,13 +5047,13 @@
         <v>62</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E202" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -5061,13 +5061,13 @@
         <v>62</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E203" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -5075,13 +5075,13 @@
         <v>62</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E204" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -5089,13 +5089,13 @@
         <v>62</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E205" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5103,13 +5103,13 @@
         <v>62</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E206" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -5117,13 +5117,13 @@
         <v>62</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E207" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -5131,13 +5131,13 @@
         <v>62</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E208" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -5145,13 +5145,13 @@
         <v>62</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E209" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -5159,13 +5159,13 @@
         <v>62</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E210" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -5173,13 +5173,13 @@
         <v>62</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E211" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -5187,13 +5187,13 @@
         <v>62</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E212" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -5201,13 +5201,13 @@
         <v>62</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E213" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
@@ -5215,13 +5215,13 @@
         <v>62</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E214" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -5229,13 +5229,13 @@
         <v>62</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E215" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -5243,13 +5243,13 @@
         <v>67</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F217" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -5257,13 +5257,13 @@
         <v>67</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F218" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -5271,13 +5271,13 @@
         <v>67</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F219" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -5285,13 +5285,13 @@
         <v>67</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F220" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -5299,13 +5299,13 @@
         <v>67</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F221" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -5313,13 +5313,13 @@
         <v>67</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F222" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -5327,13 +5327,13 @@
         <v>67</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F223" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -5341,13 +5341,13 @@
         <v>67</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F224" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -5355,13 +5355,13 @@
         <v>67</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F225" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -5369,13 +5369,13 @@
         <v>67</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F226" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -5383,13 +5383,13 @@
         <v>67</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F227" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -5397,13 +5397,13 @@
         <v>67</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F228" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -5411,13 +5411,13 @@
         <v>67</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F229" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -5425,13 +5425,13 @@
         <v>67</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F230" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -5439,13 +5439,13 @@
         <v>67</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F231" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -5453,13 +5453,13 @@
         <v>67</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F232" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -5467,13 +5467,13 @@
         <v>67</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F233" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -5481,13 +5481,13 @@
         <v>67</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F234" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -5495,13 +5495,13 @@
         <v>67</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F235" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -5509,13 +5509,13 @@
         <v>67</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F236" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -5523,13 +5523,13 @@
         <v>67</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F237" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -5537,13 +5537,13 @@
         <v>67</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F238" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -5551,13 +5551,13 @@
         <v>67</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F239" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -5565,13 +5565,13 @@
         <v>67</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F240" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -5579,13 +5579,13 @@
         <v>67</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F241" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -5593,13 +5593,13 @@
         <v>67</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F242" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -5607,13 +5607,13 @@
         <v>67</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F243" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -5621,13 +5621,13 @@
         <v>67</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F244" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -5635,13 +5635,13 @@
         <v>67</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F245" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -5649,13 +5649,13 @@
         <v>67</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F246" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -5663,13 +5663,13 @@
         <v>67</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F247" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -5677,13 +5677,13 @@
         <v>67</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F248" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -5691,13 +5691,13 @@
         <v>67</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F249" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -5705,13 +5705,13 @@
         <v>67</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F250" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -5719,13 +5719,13 @@
         <v>67</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F251" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -5733,13 +5733,13 @@
         <v>67</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F252" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -5747,13 +5747,13 @@
         <v>67</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F253" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -5761,13 +5761,13 @@
         <v>67</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F254" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -5775,13 +5775,13 @@
         <v>67</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F255" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -5789,13 +5789,13 @@
         <v>67</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F256" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -5803,13 +5803,13 @@
         <v>67</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F257" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -5817,13 +5817,13 @@
         <v>67</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F258" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -5831,13 +5831,13 @@
         <v>67</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F259" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -5845,13 +5845,13 @@
         <v>67</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F260" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -5859,13 +5859,13 @@
         <v>67</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F261" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -5873,13 +5873,13 @@
         <v>67</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F262" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -5887,13 +5887,13 @@
         <v>67</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F263" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -5901,13 +5901,13 @@
         <v>67</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F264" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -5915,13 +5915,13 @@
         <v>67</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F265" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -5929,13 +5929,13 @@
         <v>67</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F266" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -5943,13 +5943,13 @@
         <v>67</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F267" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -5957,13 +5957,13 @@
         <v>67</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F268" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -5971,13 +5971,13 @@
         <v>67</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F269" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -5985,13 +5985,13 @@
         <v>67</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F270" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -5999,13 +5999,13 @@
         <v>67</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F271" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -6013,13 +6013,13 @@
         <v>67</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F272" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -6027,13 +6027,13 @@
         <v>67</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F273" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -6041,13 +6041,13 @@
         <v>67</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F274" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -6055,13 +6055,13 @@
         <v>67</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F275" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -6069,13 +6069,13 @@
         <v>67</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F276" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -6083,13 +6083,13 @@
         <v>67</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F277" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -6097,13 +6097,13 @@
         <v>67</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F278" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -6111,13 +6111,13 @@
         <v>67</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F279" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -6125,13 +6125,13 @@
         <v>67</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F280" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -6139,13 +6139,13 @@
         <v>67</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F281" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -6153,13 +6153,13 @@
         <v>67</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F282" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -6167,13 +6167,13 @@
         <v>67</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F283" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -6181,13 +6181,13 @@
         <v>67</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F284" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -6195,13 +6195,13 @@
         <v>67</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F285" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -6209,13 +6209,13 @@
         <v>67</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F286" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -6223,13 +6223,13 @@
         <v>67</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F287" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -6237,13 +6237,13 @@
         <v>67</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F288" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -6251,13 +6251,13 @@
         <v>67</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F289" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -6265,13 +6265,13 @@
         <v>67</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F290" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -6279,13 +6279,13 @@
         <v>67</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F291" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -6293,13 +6293,13 @@
         <v>67</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F292" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -6307,13 +6307,13 @@
         <v>67</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F293" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -6321,13 +6321,13 @@
         <v>67</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F294" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -6335,13 +6335,13 @@
         <v>67</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F295" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -6349,13 +6349,13 @@
         <v>67</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F296" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -6363,13 +6363,13 @@
         <v>67</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F297" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -6377,13 +6377,13 @@
         <v>67</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F298" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -6391,13 +6391,13 @@
         <v>67</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F299" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -6405,13 +6405,13 @@
         <v>67</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F300" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -6419,13 +6419,13 @@
         <v>67</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F301" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -6433,13 +6433,13 @@
         <v>67</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F302" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -6447,13 +6447,13 @@
         <v>67</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F303" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -6461,13 +6461,13 @@
         <v>67</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F304" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -6475,13 +6475,13 @@
         <v>67</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F305" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -6489,13 +6489,13 @@
         <v>67</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F306" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -6503,13 +6503,13 @@
         <v>67</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F307" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -6517,13 +6517,13 @@
         <v>67</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F308" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -6531,13 +6531,13 @@
         <v>67</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F309" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -6545,13 +6545,13 @@
         <v>67</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F310" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -6559,13 +6559,13 @@
         <v>67</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F311" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -6573,13 +6573,13 @@
         <v>67</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F312" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -6587,13 +6587,13 @@
         <v>67</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F313" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -6601,13 +6601,13 @@
         <v>67</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F314" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -6615,13 +6615,13 @@
         <v>67</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F315" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -6629,13 +6629,13 @@
         <v>67</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F316" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -6643,13 +6643,13 @@
         <v>67</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F317" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -6657,13 +6657,13 @@
         <v>67</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F318" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -6671,13 +6671,13 @@
         <v>67</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F319" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -6685,13 +6685,13 @@
         <v>67</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F320" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -6699,13 +6699,13 @@
         <v>67</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F321" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -6713,13 +6713,13 @@
         <v>67</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F322" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -6727,13 +6727,13 @@
         <v>67</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F323" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -6741,13 +6741,13 @@
         <v>67</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F324" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -6755,13 +6755,13 @@
         <v>67</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F325" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -6769,13 +6769,13 @@
         <v>67</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F326" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -6783,13 +6783,13 @@
         <v>67</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F327" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -6797,13 +6797,13 @@
         <v>67</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F328" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -6811,13 +6811,13 @@
         <v>67</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F329" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -6825,13 +6825,13 @@
         <v>67</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F330" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -6839,13 +6839,13 @@
         <v>67</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F331" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -6853,13 +6853,13 @@
         <v>67</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F332" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -6867,13 +6867,13 @@
         <v>67</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F333" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -6881,13 +6881,13 @@
         <v>67</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F334" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -6895,13 +6895,13 @@
         <v>67</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F335" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -6909,13 +6909,13 @@
         <v>67</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F336" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -6923,13 +6923,13 @@
         <v>67</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F337" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -6937,13 +6937,13 @@
         <v>67</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F338" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -6951,13 +6951,13 @@
         <v>67</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F339" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -6965,13 +6965,13 @@
         <v>67</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F340" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -6979,13 +6979,13 @@
         <v>67</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F341" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -6993,13 +6993,13 @@
         <v>67</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F342" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -7007,13 +7007,13 @@
         <v>67</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F343" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -7021,13 +7021,13 @@
         <v>67</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F344" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -7035,13 +7035,13 @@
         <v>67</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F345" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -7049,13 +7049,13 @@
         <v>67</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F346" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -7063,13 +7063,13 @@
         <v>67</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F347" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -7077,13 +7077,13 @@
         <v>67</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F348" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -7091,13 +7091,13 @@
         <v>67</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F349" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -7105,13 +7105,13 @@
         <v>67</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F350" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -7119,13 +7119,13 @@
         <v>67</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F351" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -7133,13 +7133,13 @@
         <v>67</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F352" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -7147,13 +7147,13 @@
         <v>67</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F353" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -7161,13 +7161,13 @@
         <v>67</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F354" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -7175,13 +7175,13 @@
         <v>67</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F355" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -7189,13 +7189,13 @@
         <v>67</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F356" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -7203,13 +7203,13 @@
         <v>67</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F357" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -7217,13 +7217,13 @@
         <v>67</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F358" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -7231,13 +7231,13 @@
         <v>67</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F359" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -7245,13 +7245,13 @@
         <v>67</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F360" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -7259,13 +7259,13 @@
         <v>67</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F361" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -7273,13 +7273,13 @@
         <v>67</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F362" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -7287,13 +7287,13 @@
         <v>67</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F363" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -7301,13 +7301,13 @@
         <v>67</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F364" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -7315,13 +7315,13 @@
         <v>67</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F365" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -7329,13 +7329,13 @@
         <v>67</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F366" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -7343,13 +7343,13 @@
         <v>67</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F367" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -7357,13 +7357,13 @@
         <v>67</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F368" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -7371,13 +7371,13 @@
         <v>67</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F369" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -7385,13 +7385,13 @@
         <v>67</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F370" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -7399,13 +7399,13 @@
         <v>67</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F371" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -7413,13 +7413,13 @@
         <v>67</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F372" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -7427,13 +7427,13 @@
         <v>67</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F373" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -7441,13 +7441,13 @@
         <v>67</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F374" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -7455,13 +7455,13 @@
         <v>67</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F375" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -7469,13 +7469,13 @@
         <v>67</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F376" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -7483,13 +7483,13 @@
         <v>67</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F377" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -7497,13 +7497,13 @@
         <v>67</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F378" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -7511,13 +7511,13 @@
         <v>67</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F379" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -7525,13 +7525,13 @@
         <v>67</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F380" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -7567,10 +7567,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>69</v>
+        <v>441</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>68</v>
+        <v>440</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>21</v>
